--- a/data/trans_dic/IP29_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP29_R-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con lactancia materna exclusiva hasta los 6 primeros meses de vida o más</t>
+          <t>Menores con lactancia materna exclusiva hasta los 6 primeros meses de vida o más (tasa de respuesta: 98,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,62; 40,17</t>
+          <t>24,4; 39,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,36; 35,26</t>
+          <t>22,27; 35,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,44; 42,98</t>
+          <t>29,73; 43,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,03; 34,74</t>
+          <t>21,94; 35,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,7; 28,09</t>
+          <t>16,13; 28,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,5; 30,76</t>
+          <t>18,34; 30,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,59; 35,11</t>
+          <t>25,2; 35,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,8; 29,85</t>
+          <t>20,67; 29,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,08; 35,09</t>
+          <t>25,91; 35,3</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,39; 33,98</t>
+          <t>24,8; 34,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,41; 29,74</t>
+          <t>20,85; 29,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,03; 35,72</t>
+          <t>25,29; 34,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,69; 35,93</t>
+          <t>26,84; 36,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,9; 29,79</t>
+          <t>20,69; 29,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,46; 36,69</t>
+          <t>27,2; 36,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,22; 33,72</t>
+          <t>26,8; 33,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,09; 28,35</t>
+          <t>21,99; 28,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27,41; 34,52</t>
+          <t>27,52; 34,78</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,27; 40,03</t>
+          <t>25,67; 40,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,74; 37,28</t>
+          <t>25,19; 37,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,81; 30,24</t>
+          <t>20,0; 30,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,92; 26,26</t>
+          <t>15,43; 26,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,39; 28,21</t>
+          <t>16,85; 27,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,54; 41,61</t>
+          <t>30,32; 42,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,43; 31,05</t>
+          <t>21,69; 30,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22,55; 30,87</t>
+          <t>23,13; 31,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,63; 34,34</t>
+          <t>26,43; 34,49</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,61; 38,17</t>
+          <t>27,63; 38,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,65; 30,11</t>
+          <t>19,51; 30,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,09; 33,83</t>
+          <t>22,25; 33,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,16; 36,67</t>
+          <t>26,67; 36,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,85; 30,97</t>
+          <t>20,22; 31,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,54; 31,94</t>
+          <t>20,24; 31,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,17; 36,05</t>
+          <t>28,49; 36,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,27; 29,29</t>
+          <t>21,32; 29,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,0; 31,32</t>
+          <t>22,98; 31,14</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,5; 34,17</t>
+          <t>28,75; 34,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24,09; 29,57</t>
+          <t>24,47; 29,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,45; 32,11</t>
+          <t>26,39; 31,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,83; 31,49</t>
+          <t>25,89; 31,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,33; 26,42</t>
+          <t>21,24; 26,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,57; 33,49</t>
+          <t>27,66; 33,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,97; 32,08</t>
+          <t>28,14; 32,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,35; 27,35</t>
+          <t>23,44; 27,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,83; 31,77</t>
+          <t>27,68; 31,76</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores con lactancia materna exclusiva hasta los 6 primeros meses de vida o más (tasa de respuesta: 98,65%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>30238</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>38909</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>44472</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>29799</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>29179</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>29312</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>60037</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>68088</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>73784</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>23035; 37394</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>30326; 48344</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>36445; 53618</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>23356; 37962</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>21947; 38821</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>22087; 37283</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>50616; 72056</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>56262; 80451</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>62959; 85767</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>73035</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>58948</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>63171</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>77988</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>65932</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>81397</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>151022</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>124880</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>144568</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>61340; 84768</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>48994; 70368</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>52779; 72909</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>67168; 91121</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>54817; 78752</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>69646; 94142</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>133336; 167312</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>109926; 141888</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>127894; 161616</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>40046</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>48986</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>46059</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>27396</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>34675</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>66746</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>67441</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>83661</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>112805</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>31464; 49194</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>39555; 58875</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>37788; 57191</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>21098; 36404</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>26252; 43303</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>55903; 77477</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>56244; 78478</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>72357; 97864</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>98650; 128736</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>61781</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>41068</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>46079</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>63652</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>44697</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>43300</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>125433</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>85765</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>89379</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>52073; 72130</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>32592; 51096</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>36980; 55809</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>53873; 74650</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>35709; 54808</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>33677; 52511</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>111251; 141134</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>73262; 100115</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>76400; 103557</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>205100</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>187911</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>199781</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>198834</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>174484</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>220754</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>403934</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>362394</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>420535</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>187669; 226564</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>170146; 207315</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>181116; 217984</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>180081; 218392</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>155737; 194490</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>201162; 240839</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>379329; 433388</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>334877; 392290</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>391273; 448977</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP29_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP29_R-Edad-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,4; 39,61</t>
+          <t>24,69; 40,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,27; 35,51</t>
+          <t>22,53; 35,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,73; 43,74</t>
+          <t>29,39; 43,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,94; 35,66</t>
+          <t>20,73; 34,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,13; 28,53</t>
+          <t>15,94; 28,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,34; 30,97</t>
+          <t>18,63; 31,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,2; 35,87</t>
+          <t>25,05; 35,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,67; 29,55</t>
+          <t>20,98; 29,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25,91; 35,3</t>
+          <t>25,91; 35,52</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,8; 34,27</t>
+          <t>24,81; 34,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,85; 29,94</t>
+          <t>20,68; 29,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,29; 34,94</t>
+          <t>25,76; 35,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,84; 36,41</t>
+          <t>26,46; 36,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,69; 29,73</t>
+          <t>20,47; 29,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,2; 36,77</t>
+          <t>27,48; 36,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,8; 33,62</t>
+          <t>27,04; 33,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,99; 28,38</t>
+          <t>21,93; 28,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27,52; 34,78</t>
+          <t>28,02; 35,56</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,67; 40,14</t>
+          <t>25,94; 39,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,19; 37,49</t>
+          <t>25,14; 37,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,0; 30,28</t>
+          <t>19,72; 29,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,43; 26,62</t>
+          <t>15,33; 25,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,85; 27,79</t>
+          <t>16,96; 28,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,32; 42,03</t>
+          <t>30,66; 41,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,69; 30,27</t>
+          <t>21,96; 30,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,13; 31,28</t>
+          <t>23,05; 31,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,43; 34,49</t>
+          <t>26,18; 34,31</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,63; 38,28</t>
+          <t>27,42; 38,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,51; 30,59</t>
+          <t>19,43; 30,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,25; 33,59</t>
+          <t>22,53; 34,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,67; 36,95</t>
+          <t>26,72; 37,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,22; 31,04</t>
+          <t>20,7; 31,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,24; 31,57</t>
+          <t>20,5; 32,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,49; 36,15</t>
+          <t>28,3; 36,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,32; 29,14</t>
+          <t>21,5; 29,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,98; 31,14</t>
+          <t>23,45; 31,81</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,75; 34,71</t>
+          <t>28,54; 34,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24,47; 29,82</t>
+          <t>24,12; 29,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,39; 31,76</t>
+          <t>26,51; 31,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,89; 31,4</t>
+          <t>25,99; 31,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,24; 26,52</t>
+          <t>21,2; 26,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,66; 33,12</t>
+          <t>27,26; 33,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,14; 32,15</t>
+          <t>28,15; 32,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,44; 27,46</t>
+          <t>23,61; 27,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,68; 31,76</t>
+          <t>27,66; 31,72</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23035; 37394</t>
+          <t>23314; 38001</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30326; 48344</t>
+          <t>30681; 48076</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36445; 53618</t>
+          <t>36033; 53231</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23356; 37962</t>
+          <t>22065; 37225</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21947; 38821</t>
+          <t>21684; 38525</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22087; 37283</t>
+          <t>22432; 37911</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50616; 72056</t>
+          <t>50322; 70858</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>56262; 80451</t>
+          <t>57096; 81180</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62959; 85767</t>
+          <t>62958; 86314</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>61340; 84768</t>
+          <t>61371; 84648</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>48994; 70368</t>
+          <t>48593; 69333</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52779; 72909</t>
+          <t>53748; 74236</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67168; 91121</t>
+          <t>66215; 90602</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54817; 78752</t>
+          <t>54225; 77819</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>69646; 94142</t>
+          <t>70348; 94630</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>133336; 167312</t>
+          <t>134532; 165582</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>109926; 141888</t>
+          <t>109620; 142989</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>127894; 161616</t>
+          <t>130213; 165237</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31464; 49194</t>
+          <t>31796; 48757</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39555; 58875</t>
+          <t>39486; 59093</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37788; 57191</t>
+          <t>37256; 55837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21098; 36404</t>
+          <t>20955; 35412</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>26252; 43303</t>
+          <t>26423; 43800</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>55903; 77477</t>
+          <t>56532; 77139</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>56244; 78478</t>
+          <t>56937; 79533</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>72357; 97864</t>
+          <t>72126; 98894</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>98650; 128736</t>
+          <t>97735; 128078</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>52073; 72130</t>
+          <t>51664; 71839</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32592; 51096</t>
+          <t>32449; 50506</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36980; 55809</t>
+          <t>37440; 56903</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53873; 74650</t>
+          <t>53978; 74944</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35709; 54808</t>
+          <t>36552; 55657</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33677; 52511</t>
+          <t>34109; 53991</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>111251; 141134</t>
+          <t>110494; 141397</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>73262; 100115</t>
+          <t>73888; 99881</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>76400; 103557</t>
+          <t>77963; 105771</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>187669; 226564</t>
+          <t>186301; 225741</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>170146; 207315</t>
+          <t>167710; 207091</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>181116; 217984</t>
+          <t>181939; 218783</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>180081; 218392</t>
+          <t>180744; 218650</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>155737; 194490</t>
+          <t>155443; 193585</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>201162; 240839</t>
+          <t>198247; 240145</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>379329; 433388</t>
+          <t>379490; 432192</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>334877; 392290</t>
+          <t>337279; 388911</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>391273; 448977</t>
+          <t>390945; 448340</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP29_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP29_R-Edad-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>27,99%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21,45%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24,35%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>32,03%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>28,58%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>36,28%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>27,99%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>21,45%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>24,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,69; 40,25</t>
+          <t>21,03; 34,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,53; 35,31</t>
+          <t>15,7; 28,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,39; 43,42</t>
+          <t>18,5; 30,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,73; 34,97</t>
+          <t>24,62; 40,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,94; 28,32</t>
+          <t>22,36; 35,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,63; 31,49</t>
+          <t>28,44; 42,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,05; 35,28</t>
+          <t>24,59; 35,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,98; 29,82</t>
+          <t>20,8; 29,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25,91; 35,52</t>
+          <t>26,08; 35,09</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>31,16%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24,89%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>31,79%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>29,53%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>25,08%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>30,27%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>31,16%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>24,89%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>31,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,81; 34,22</t>
+          <t>26,69; 35,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,68; 29,5</t>
+          <t>20,9; 29,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,76; 35,57</t>
+          <t>27,46; 36,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,46; 36,21</t>
+          <t>25,39; 33,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,47; 29,38</t>
+          <t>20,41; 29,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,48; 36,96</t>
+          <t>25,03; 35,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,04; 33,28</t>
+          <t>27,22; 33,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,93; 28,6</t>
+          <t>22,09; 28,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,02; 35,56</t>
+          <t>27,41; 34,52</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20,04%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>22,25%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>36,2%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>32,67%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>31,19%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>24,38%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>20,04%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>22,25%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>36,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,94; 39,78</t>
+          <t>14,92; 26,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,14; 37,63</t>
+          <t>17,39; 28,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,72; 29,56</t>
+          <t>30,54; 41,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,33; 25,9</t>
+          <t>26,27; 40,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,96; 28,11</t>
+          <t>25,74; 37,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,66; 41,84</t>
+          <t>19,81; 30,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,96; 30,67</t>
+          <t>21,43; 31,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,05; 31,61</t>
+          <t>22,55; 30,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,18; 34,31</t>
+          <t>26,63; 34,34</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>31,51%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25,31%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26,03%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>32,79%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>24,59%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>27,73%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>31,51%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>25,31%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>26,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,42; 38,12</t>
+          <t>26,16; 36,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,43; 30,24</t>
+          <t>19,85; 30,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,53; 34,24</t>
+          <t>20,54; 31,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,72; 37,1</t>
+          <t>27,61; 38,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,7; 31,52</t>
+          <t>19,65; 30,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,5; 32,46</t>
+          <t>22,09; 33,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,3; 36,21</t>
+          <t>28,17; 36,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,5; 29,07</t>
+          <t>21,27; 29,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,45; 31,81</t>
+          <t>23,0; 31,32</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>28,59%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>23,79%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>30,36%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>31,42%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>27,03%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>29,11%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>28,59%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>23,79%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>30,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,54; 34,58</t>
+          <t>25,83; 31,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24,12; 29,79</t>
+          <t>21,33; 26,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,51; 31,88</t>
+          <t>27,57; 33,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,99; 31,44</t>
+          <t>28,5; 34,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,2; 26,4</t>
+          <t>24,09; 29,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,26; 33,03</t>
+          <t>26,45; 32,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,15; 32,06</t>
+          <t>27,97; 32,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,61; 27,22</t>
+          <t>23,35; 27,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,66; 31,72</t>
+          <t>27,83; 31,77</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1316,27 +1316,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>69</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>29799</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>29179</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>29312</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>30238</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>38909</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>44472</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>29799</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>29179</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>29312</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23314; 38001</t>
+          <t>22387; 36981</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30681; 48076</t>
+          <t>21366; 38212</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36033; 53231</t>
+          <t>22273; 37036</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22065; 37225</t>
+          <t>23244; 37926</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21684; 38525</t>
+          <t>30443; 48003</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22432; 37911</t>
+          <t>34862; 52686</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50322; 70858</t>
+          <t>49392; 70522</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>57096; 81180</t>
+          <t>56615; 81260</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62958; 86314</t>
+          <t>63376; 85271</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>99</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>77988</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>65932</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>81397</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>73035</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>58948</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>63171</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>77988</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>65932</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>81397</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>61371; 84648</t>
+          <t>66788; 89906</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>48593; 69333</t>
+          <t>55362; 78917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53748; 74236</t>
+          <t>70300; 93940</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>66215; 90602</t>
+          <t>62808; 84044</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54225; 77819</t>
+          <t>47972; 69877</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>70348; 94630</t>
+          <t>52226; 74536</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>134532; 165582</t>
+          <t>135467; 167771</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>109620; 142989</t>
+          <t>110410; 141708</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>130213; 165237</t>
+          <t>127372; 160417</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>66</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>27396</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>34675</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>66746</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>40046</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>48986</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>46059</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>27396</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>34675</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>66746</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31796; 48757</t>
+          <t>20403; 35900</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39486; 59093</t>
+          <t>27104; 43956</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37256; 55837</t>
+          <t>56299; 76705</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20955; 35412</t>
+          <t>32199; 49067</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>26423; 43800</t>
+          <t>40417; 58544</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>56532; 77139</t>
+          <t>37421; 57131</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>56937; 79533</t>
+          <t>55563; 80510</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>72126; 98894</t>
+          <t>70553; 96585</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>97735; 128078</t>
+          <t>99388; 128162</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>67</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>63652</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>44697</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>43300</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>61781</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>41068</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>46079</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>63652</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>44697</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>43300</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>51664; 71839</t>
+          <t>52839; 74066</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32449; 50506</t>
+          <t>35054; 54681</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37440; 56903</t>
+          <t>34174; 53139</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53978; 74944</t>
+          <t>52030; 71930</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36552; 55657</t>
+          <t>32812; 50280</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34109; 53991</t>
+          <t>36705; 56208</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>110494; 141397</t>
+          <t>110007; 140758</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>73888; 99881</t>
+          <t>73097; 100648</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>77963; 105771</t>
+          <t>76472; 104129</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>306</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>269</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>301</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>198834</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>174484</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>220754</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>205100</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>187911</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>199781</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>198834</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>174484</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>220754</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>186301; 225741</t>
+          <t>179601; 218963</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>167710; 207091</t>
+          <t>156425; 193734</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>181939; 218783</t>
+          <t>200495; 243531</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>180744; 218650</t>
+          <t>186056; 223047</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>155443; 193585</t>
+          <t>167451; 205543</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>198247; 240145</t>
+          <t>181532; 220370</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>379490; 432192</t>
+          <t>377129; 432518</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>337279; 388911</t>
+          <t>333567; 390742</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>390945; 448340</t>
+          <t>393370; 449071</t>
         </is>
       </c>
     </row>
